--- a/data/processed/temporadas.xlsx
+++ b/data/processed/temporadas.xlsx
@@ -424,27 +424,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>id_competicao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id_vencedor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>data_inicio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>data_fim</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rodada_atual</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id_vencedor</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>nome_vencedor</t>
         </is>
       </c>
     </row>
@@ -452,223 +452,227 @@
       <c r="A2" t="n">
         <v>2474</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>19</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2371</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>29/03/2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21/12/2025</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>38</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2257</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13/04/2024</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>08/12/2024</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>38</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>1557</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2023-04-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2023-12-03</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15/04/2023</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>03/12/2023</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>37</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1377</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10/04/2022</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>13/11/2022</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>38</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>726</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2021-05-30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30/05/2021</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>05/12/2021</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>37</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>589</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>09/08/2020</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>24/02/2021</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CR Flamengo</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>460</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2019-04-28</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2019-12-08</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28/04/2019</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>08/12/2019</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>38</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CR Flamengo</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>15</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2018-12-02</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="B10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14/04/2018</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02/12/2018</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>38</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1769</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SE Palmeiras</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>459</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2017-05-13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2017-12-03</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
+      <c r="B11" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C11" t="n">
         <v>1779</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SC Corinthians Paulista</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13/05/2017</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>03/12/2017</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/temporadas.xlsx
+++ b/data/processed/temporadas.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,22 +433,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>id_vencedor</t>
+          <t>ano_inicio</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>ano_fim</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>data_fim</t>
+          <t>data_inicio_completa</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>rodada_atual</t>
+          <t>data_fim_completa</t>
         </is>
       </c>
     </row>
@@ -455,224 +459,18 @@
       <c r="B2" t="n">
         <v>2013</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>28/01/2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2371</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>29/03/2025</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21/12/2025</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2257</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>13/04/2024</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>08/12/2024</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1557</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>15/04/2023</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>03/12/2023</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10/04/2022</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>13/11/2022</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>726</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>30/05/2021</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>05/12/2021</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>589</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1783</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>09/08/2020</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>24/02/2021</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>460</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1783</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>28/04/2019</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>08/12/2019</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1769</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>14/04/2018</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>02/12/2018</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>459</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1779</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>13/05/2017</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>03/12/2017</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>46358</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
